--- a/database/data/RAW FILE EMPLOYEE ALL.xlsx
+++ b/database/data/RAW FILE EMPLOYEE ALL.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MAMP\htdocs\sigarda.kemenagpessel.com\storage\app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MAMP\htdocs\sigarda.kemenagpessel.com\database\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B629F260-F9D2-4EF6-9016-1418C1B0C920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C6D7D1-FFE5-4F83-B70B-A36F7341692C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0F5AAECB-9CA1-44EA-849B-3A26CA678E71}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">employees_pns_minimal_with_kode!$A$1:$F$1565</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">employees_pns_minimal_with_kode!$A$1:$F$1596</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14085" uniqueCount="3792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14178" uniqueCount="3859">
   <si>
     <t>nip</t>
   </si>
@@ -11424,6 +11424,207 @@
   </si>
   <si>
     <t>2055-02-01</t>
+  </si>
+  <si>
+    <t>‌PENGADMINISTRASI PERKANTORAN</t>
+  </si>
+  <si>
+    <t>198910232025212057</t>
+  </si>
+  <si>
+    <t>‌ADE OKTAVIA</t>
+  </si>
+  <si>
+    <t>199807222025211029</t>
+  </si>
+  <si>
+    <t>‌ADHITYA</t>
+  </si>
+  <si>
+    <t>‌PENATA LAYANAN OPERASIONAL</t>
+  </si>
+  <si>
+    <t>198604242025211083</t>
+  </si>
+  <si>
+    <t>‌AFRIZAL MIMORA</t>
+  </si>
+  <si>
+    <t>‌PENGELOLA UMUM OPERASIONAL</t>
+  </si>
+  <si>
+    <t>199905242025212040</t>
+  </si>
+  <si>
+    <t>‌ANISA RAHMA YANTI</t>
+  </si>
+  <si>
+    <t>200107062025211014</t>
+  </si>
+  <si>
+    <t>‌BENI JULIANSYA</t>
+  </si>
+  <si>
+    <t>198306012025212045</t>
+  </si>
+  <si>
+    <t>‌DEVIT MARLINDA</t>
+  </si>
+  <si>
+    <t>‌GURU AHLI PERTAMA - GURU AKIDAH AKHLAQ</t>
+  </si>
+  <si>
+    <t>197510072025212017</t>
+  </si>
+  <si>
+    <t>‌ERLI ZARNITA</t>
+  </si>
+  <si>
+    <t>199408182025211070</t>
+  </si>
+  <si>
+    <t>‌FALDI MAULANA</t>
+  </si>
+  <si>
+    <t>200209112025211007</t>
+  </si>
+  <si>
+    <t>‌FAUZAN FADDATURRAHMAN</t>
+  </si>
+  <si>
+    <t>199002022025212093</t>
+  </si>
+  <si>
+    <t>‌FEBRILISA</t>
+  </si>
+  <si>
+    <t>198008212025212020</t>
+  </si>
+  <si>
+    <t>‌FITRI YESI</t>
+  </si>
+  <si>
+    <t>‌PENGELOLA LAYANAN OPERASIONAL</t>
+  </si>
+  <si>
+    <t>198012312025211119</t>
+  </si>
+  <si>
+    <t>‌HARIYANTO</t>
+  </si>
+  <si>
+    <t>199102262025211045</t>
+  </si>
+  <si>
+    <t>‌HARLAN MARDIYAN</t>
+  </si>
+  <si>
+    <t>198203312025212024</t>
+  </si>
+  <si>
+    <t>‌ISNA MARLENI</t>
+  </si>
+  <si>
+    <t>199711302025211039</t>
+  </si>
+  <si>
+    <t>‌KRYS SOPER</t>
+  </si>
+  <si>
+    <t>199904102025211023</t>
+  </si>
+  <si>
+    <t>‌M. MICHAEL DUTA</t>
+  </si>
+  <si>
+    <t>200002282025212038</t>
+  </si>
+  <si>
+    <t>‌MARDIYANA</t>
+  </si>
+  <si>
+    <t>198103212025212032</t>
+  </si>
+  <si>
+    <t>‌MITRA WATI</t>
+  </si>
+  <si>
+    <t>198303132025212061</t>
+  </si>
+  <si>
+    <t>‌PITRI AYANI</t>
+  </si>
+  <si>
+    <t>199901182025212023</t>
+  </si>
+  <si>
+    <t>‌RAMADHANI FITRI</t>
+  </si>
+  <si>
+    <t>199401172025211043</t>
+  </si>
+  <si>
+    <t>‌RIDHO IRFAL</t>
+  </si>
+  <si>
+    <t>200110242025212017</t>
+  </si>
+  <si>
+    <t>‌SITI NUR HAILAH SAFITRI</t>
+  </si>
+  <si>
+    <t>198502022025211086</t>
+  </si>
+  <si>
+    <t>‌WENDRA TAUFIT</t>
+  </si>
+  <si>
+    <t>198605182025212053</t>
+  </si>
+  <si>
+    <t>‌WENI ENDESI</t>
+  </si>
+  <si>
+    <t>198706072025212073</t>
+  </si>
+  <si>
+    <t>‌WESI SUSANTI</t>
+  </si>
+  <si>
+    <t>199102222025212062</t>
+  </si>
+  <si>
+    <t>‌WILDA HERLINA</t>
+  </si>
+  <si>
+    <t>198102122025212035</t>
+  </si>
+  <si>
+    <t>‌YANTI SUSANTI</t>
+  </si>
+  <si>
+    <t>199706262025212055</t>
+  </si>
+  <si>
+    <t>‌YUNIFA PUTRI ASKA</t>
+  </si>
+  <si>
+    <t>196912092025211011</t>
+  </si>
+  <si>
+    <t>‌ZAMAUN</t>
+  </si>
+  <si>
+    <t>199909012025212043</t>
+  </si>
+  <si>
+    <t>‌ZHAHARA YUSRA</t>
+  </si>
+  <si>
+    <t>198407022025211061</t>
+  </si>
+  <si>
+    <t>‌ZULHENDRI</t>
   </si>
 </sst>
 </file>
@@ -11459,8 +11660,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11528,7 +11730,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6F756D7C-5373-440F-9D38-790C073ACF90}" name="employees_pns_minimal_with_kodesatker" displayName="employees_pns_minimal_with_kodesatker" ref="A1:I1565" tableType="queryTable" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6F756D7C-5373-440F-9D38-790C073ACF90}" name="employees_pns_minimal_with_kodesatker" displayName="employees_pns_minimal_with_kodesatker" ref="A1:I1596" tableType="queryTable" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{183E0704-311A-4ED2-A39C-4975328733C9}" uniqueName="1" name="nip" queryTableFieldId="1" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{9180AB27-6B1C-401D-9FF7-574184D844E3}" uniqueName="2" name="full_name" queryTableFieldId="2" dataDxfId="7"/>
@@ -11861,7 +12063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE636EC-43D0-4D50-A6C3-192BAE669146}">
-  <dimension ref="A1:I1565"/>
+  <dimension ref="A1:I1596"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -57259,6 +57461,533 @@
       <c r="I1565" t="s">
         <v>3791</v>
       </c>
+    </row>
+    <row r="1566" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1566" s="1" t="s">
+        <v>3793</v>
+      </c>
+      <c r="B1566" s="1" t="s">
+        <v>3794</v>
+      </c>
+      <c r="C1566" s="1" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1566" s="1"/>
+      <c r="E1566" s="1"/>
+      <c r="F1566" s="1"/>
+      <c r="G1566" s="1"/>
+      <c r="H1566" s="1"/>
+      <c r="I1566" s="1"/>
+    </row>
+    <row r="1567" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1567" s="1" t="s">
+        <v>3795</v>
+      </c>
+      <c r="B1567" s="1" t="s">
+        <v>3796</v>
+      </c>
+      <c r="C1567" s="1" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D1567" s="1"/>
+      <c r="E1567" s="1"/>
+      <c r="F1567" s="1"/>
+      <c r="G1567" s="1"/>
+      <c r="H1567" s="1"/>
+      <c r="I1567" s="1"/>
+    </row>
+    <row r="1568" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1568" s="1" t="s">
+        <v>3798</v>
+      </c>
+      <c r="B1568" s="1" t="s">
+        <v>3799</v>
+      </c>
+      <c r="C1568" s="1" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1568" s="1"/>
+      <c r="E1568" s="1"/>
+      <c r="F1568" s="1"/>
+      <c r="G1568" s="1"/>
+      <c r="H1568" s="1"/>
+      <c r="I1568" s="1"/>
+    </row>
+    <row r="1569" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1569" s="1" t="s">
+        <v>3801</v>
+      </c>
+      <c r="B1569" s="1" t="s">
+        <v>3802</v>
+      </c>
+      <c r="C1569" s="1" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D1569" s="1"/>
+      <c r="E1569" s="1"/>
+      <c r="F1569" s="1"/>
+      <c r="G1569" s="1"/>
+      <c r="H1569" s="1"/>
+      <c r="I1569" s="1"/>
+    </row>
+    <row r="1570" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1570" s="1" t="s">
+        <v>3803</v>
+      </c>
+      <c r="B1570" s="1" t="s">
+        <v>3804</v>
+      </c>
+      <c r="C1570" s="1" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1570" s="1"/>
+      <c r="E1570" s="1"/>
+      <c r="F1570" s="1"/>
+      <c r="G1570" s="1"/>
+      <c r="H1570" s="1"/>
+      <c r="I1570" s="1"/>
+    </row>
+    <row r="1571" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1571" s="1" t="s">
+        <v>3805</v>
+      </c>
+      <c r="B1571" s="1" t="s">
+        <v>3806</v>
+      </c>
+      <c r="C1571" s="1" t="s">
+        <v>3807</v>
+      </c>
+      <c r="D1571" s="1"/>
+      <c r="E1571" s="1"/>
+      <c r="F1571" s="1"/>
+      <c r="G1571" s="1"/>
+      <c r="H1571" s="1"/>
+      <c r="I1571" s="1"/>
+    </row>
+    <row r="1572" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1572" s="1" t="s">
+        <v>3808</v>
+      </c>
+      <c r="B1572" s="1" t="s">
+        <v>3809</v>
+      </c>
+      <c r="C1572" s="1" t="s">
+        <v>3800</v>
+      </c>
+      <c r="D1572" s="1"/>
+      <c r="E1572" s="1"/>
+      <c r="F1572" s="1"/>
+      <c r="G1572" s="1"/>
+      <c r="H1572" s="1"/>
+      <c r="I1572" s="1"/>
+    </row>
+    <row r="1573" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1573" s="1" t="s">
+        <v>3810</v>
+      </c>
+      <c r="B1573" s="1" t="s">
+        <v>3811</v>
+      </c>
+      <c r="C1573" s="1" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D1573" s="1"/>
+      <c r="E1573" s="1"/>
+      <c r="F1573" s="1"/>
+      <c r="G1573" s="1"/>
+      <c r="H1573" s="1"/>
+      <c r="I1573" s="1"/>
+    </row>
+    <row r="1574" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1574" s="1" t="s">
+        <v>3812</v>
+      </c>
+      <c r="B1574" s="1" t="s">
+        <v>3813</v>
+      </c>
+      <c r="C1574" s="1" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1574" s="1"/>
+      <c r="E1574" s="1"/>
+      <c r="F1574" s="1"/>
+      <c r="G1574" s="1"/>
+      <c r="H1574" s="1"/>
+      <c r="I1574" s="1"/>
+    </row>
+    <row r="1575" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1575" s="1" t="s">
+        <v>3814</v>
+      </c>
+      <c r="B1575" s="1" t="s">
+        <v>3815</v>
+      </c>
+      <c r="C1575" s="1" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1575" s="1"/>
+      <c r="E1575" s="1"/>
+      <c r="F1575" s="1"/>
+      <c r="G1575" s="1"/>
+      <c r="H1575" s="1"/>
+      <c r="I1575" s="1"/>
+    </row>
+    <row r="1576" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1576" s="1" t="s">
+        <v>3816</v>
+      </c>
+      <c r="B1576" s="1" t="s">
+        <v>3817</v>
+      </c>
+      <c r="C1576" s="1" t="s">
+        <v>3818</v>
+      </c>
+      <c r="D1576" s="1"/>
+      <c r="E1576" s="1"/>
+      <c r="F1576" s="1"/>
+      <c r="G1576" s="1"/>
+      <c r="H1576" s="1"/>
+      <c r="I1576" s="1"/>
+    </row>
+    <row r="1577" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1577" s="1" t="s">
+        <v>3819</v>
+      </c>
+      <c r="B1577" s="1" t="s">
+        <v>3820</v>
+      </c>
+      <c r="C1577" s="1" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1577" s="1"/>
+      <c r="E1577" s="1"/>
+      <c r="F1577" s="1"/>
+      <c r="G1577" s="1"/>
+      <c r="H1577" s="1"/>
+      <c r="I1577" s="1"/>
+    </row>
+    <row r="1578" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1578" s="1" t="s">
+        <v>3821</v>
+      </c>
+      <c r="B1578" s="1" t="s">
+        <v>3822</v>
+      </c>
+      <c r="C1578" s="1" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D1578" s="1"/>
+      <c r="E1578" s="1"/>
+      <c r="F1578" s="1"/>
+      <c r="G1578" s="1"/>
+      <c r="H1578" s="1"/>
+      <c r="I1578" s="1"/>
+    </row>
+    <row r="1579" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1579" s="1" t="s">
+        <v>3823</v>
+      </c>
+      <c r="B1579" s="1" t="s">
+        <v>3824</v>
+      </c>
+      <c r="C1579" s="1" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D1579" s="1"/>
+      <c r="E1579" s="1"/>
+      <c r="F1579" s="1"/>
+      <c r="G1579" s="1"/>
+      <c r="H1579" s="1"/>
+      <c r="I1579" s="1"/>
+    </row>
+    <row r="1580" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1580" s="1" t="s">
+        <v>3825</v>
+      </c>
+      <c r="B1580" s="1" t="s">
+        <v>3826</v>
+      </c>
+      <c r="C1580" s="1" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1580" s="1"/>
+      <c r="E1580" s="1"/>
+      <c r="F1580" s="1"/>
+      <c r="G1580" s="1"/>
+      <c r="H1580" s="1"/>
+      <c r="I1580" s="1"/>
+    </row>
+    <row r="1581" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1581" s="1" t="s">
+        <v>3827</v>
+      </c>
+      <c r="B1581" s="1" t="s">
+        <v>3828</v>
+      </c>
+      <c r="C1581" s="1" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D1581" s="1"/>
+      <c r="E1581" s="1"/>
+      <c r="F1581" s="1"/>
+      <c r="G1581" s="1"/>
+      <c r="H1581" s="1"/>
+      <c r="I1581" s="1"/>
+    </row>
+    <row r="1582" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1582" s="1" t="s">
+        <v>3829</v>
+      </c>
+      <c r="B1582" s="1" t="s">
+        <v>3830</v>
+      </c>
+      <c r="C1582" s="1" t="s">
+        <v>3818</v>
+      </c>
+      <c r="D1582" s="1"/>
+      <c r="E1582" s="1"/>
+      <c r="F1582" s="1"/>
+      <c r="G1582" s="1"/>
+      <c r="H1582" s="1"/>
+      <c r="I1582" s="1"/>
+    </row>
+    <row r="1583" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1583" s="1" t="s">
+        <v>3831</v>
+      </c>
+      <c r="B1583" s="1" t="s">
+        <v>3832</v>
+      </c>
+      <c r="C1583" s="1" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1583" s="1"/>
+      <c r="E1583" s="1"/>
+      <c r="F1583" s="1"/>
+      <c r="G1583" s="1"/>
+      <c r="H1583" s="1"/>
+      <c r="I1583" s="1"/>
+    </row>
+    <row r="1584" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1584" s="1" t="s">
+        <v>3833</v>
+      </c>
+      <c r="B1584" s="1" t="s">
+        <v>3834</v>
+      </c>
+      <c r="C1584" s="1" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D1584" s="1"/>
+      <c r="E1584" s="1"/>
+      <c r="F1584" s="1"/>
+      <c r="G1584" s="1"/>
+      <c r="H1584" s="1"/>
+      <c r="I1584" s="1"/>
+    </row>
+    <row r="1585" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1585" s="1" t="s">
+        <v>3835</v>
+      </c>
+      <c r="B1585" s="1" t="s">
+        <v>3836</v>
+      </c>
+      <c r="C1585" s="1" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D1585" s="1"/>
+      <c r="E1585" s="1"/>
+      <c r="F1585" s="1"/>
+      <c r="G1585" s="1"/>
+      <c r="H1585" s="1"/>
+      <c r="I1585" s="1"/>
+    </row>
+    <row r="1586" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1586" s="1" t="s">
+        <v>3837</v>
+      </c>
+      <c r="B1586" s="1" t="s">
+        <v>3838</v>
+      </c>
+      <c r="C1586" s="1" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1586" s="1"/>
+      <c r="E1586" s="1"/>
+      <c r="F1586" s="1"/>
+      <c r="G1586" s="1"/>
+      <c r="H1586" s="1"/>
+      <c r="I1586" s="1"/>
+    </row>
+    <row r="1587" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1587" s="1" t="s">
+        <v>3839</v>
+      </c>
+      <c r="B1587" s="1" t="s">
+        <v>3840</v>
+      </c>
+      <c r="C1587" s="1" t="s">
+        <v>3818</v>
+      </c>
+      <c r="D1587" s="1"/>
+      <c r="E1587" s="1"/>
+      <c r="F1587" s="1"/>
+      <c r="G1587" s="1"/>
+      <c r="H1587" s="1"/>
+      <c r="I1587" s="1"/>
+    </row>
+    <row r="1588" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1588" s="1" t="s">
+        <v>3841</v>
+      </c>
+      <c r="B1588" s="1" t="s">
+        <v>3842</v>
+      </c>
+      <c r="C1588" s="1" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1588" s="1"/>
+      <c r="E1588" s="1"/>
+      <c r="F1588" s="1"/>
+      <c r="G1588" s="1"/>
+      <c r="H1588" s="1"/>
+      <c r="I1588" s="1"/>
+    </row>
+    <row r="1589" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1589" s="1" t="s">
+        <v>3843</v>
+      </c>
+      <c r="B1589" s="1" t="s">
+        <v>3844</v>
+      </c>
+      <c r="C1589" s="1" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1589" s="1"/>
+      <c r="E1589" s="1"/>
+      <c r="F1589" s="1"/>
+      <c r="G1589" s="1"/>
+      <c r="H1589" s="1"/>
+      <c r="I1589" s="1"/>
+    </row>
+    <row r="1590" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1590" s="1" t="s">
+        <v>3845</v>
+      </c>
+      <c r="B1590" s="1" t="s">
+        <v>3846</v>
+      </c>
+      <c r="C1590" s="1" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D1590" s="1"/>
+      <c r="E1590" s="1"/>
+      <c r="F1590" s="1"/>
+      <c r="G1590" s="1"/>
+      <c r="H1590" s="1"/>
+      <c r="I1590" s="1"/>
+    </row>
+    <row r="1591" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1591" s="1" t="s">
+        <v>3847</v>
+      </c>
+      <c r="B1591" s="1" t="s">
+        <v>3848</v>
+      </c>
+      <c r="C1591" s="1" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D1591" s="1"/>
+      <c r="E1591" s="1"/>
+      <c r="F1591" s="1"/>
+      <c r="G1591" s="1"/>
+      <c r="H1591" s="1"/>
+      <c r="I1591" s="1"/>
+    </row>
+    <row r="1592" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1592" s="1" t="s">
+        <v>3849</v>
+      </c>
+      <c r="B1592" s="1" t="s">
+        <v>3850</v>
+      </c>
+      <c r="C1592" s="1" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D1592" s="1"/>
+      <c r="E1592" s="1"/>
+      <c r="F1592" s="1"/>
+      <c r="G1592" s="1"/>
+      <c r="H1592" s="1"/>
+      <c r="I1592" s="1"/>
+    </row>
+    <row r="1593" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1593" s="1" t="s">
+        <v>3851</v>
+      </c>
+      <c r="B1593" s="1" t="s">
+        <v>3852</v>
+      </c>
+      <c r="C1593" s="1" t="s">
+        <v>3797</v>
+      </c>
+      <c r="D1593" s="1"/>
+      <c r="E1593" s="1"/>
+      <c r="F1593" s="1"/>
+      <c r="G1593" s="1"/>
+      <c r="H1593" s="1"/>
+      <c r="I1593" s="1"/>
+    </row>
+    <row r="1594" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1594" s="1" t="s">
+        <v>3853</v>
+      </c>
+      <c r="B1594" s="1" t="s">
+        <v>3854</v>
+      </c>
+      <c r="C1594" s="1" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1594" s="1"/>
+      <c r="E1594" s="1"/>
+      <c r="F1594" s="1"/>
+      <c r="G1594" s="1"/>
+      <c r="H1594" s="1"/>
+      <c r="I1594" s="1"/>
+    </row>
+    <row r="1595" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1595" s="1" t="s">
+        <v>3855</v>
+      </c>
+      <c r="B1595" s="1" t="s">
+        <v>3856</v>
+      </c>
+      <c r="C1595" s="1" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1595" s="1"/>
+      <c r="E1595" s="1"/>
+      <c r="F1595" s="1"/>
+      <c r="G1595" s="1"/>
+      <c r="H1595" s="1"/>
+      <c r="I1595" s="1"/>
+    </row>
+    <row r="1596" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1596" s="1" t="s">
+        <v>3857</v>
+      </c>
+      <c r="B1596" s="1" t="s">
+        <v>3858</v>
+      </c>
+      <c r="C1596" s="1" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D1596" s="1"/>
+      <c r="E1596" s="1"/>
+      <c r="F1596" s="1"/>
+      <c r="G1596" s="1"/>
+      <c r="H1596" s="1"/>
+      <c r="I1596" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
